--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.6850106800924</v>
+        <v>14.67923642526539</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.25613160044787</v>
+        <v>15.26907170125877</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.35239519926296</v>
+        <v>13.30295411461418</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.501158781553513</v>
+        <v>1.501023710280085</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38245.41267428243</v>
+        <v>38337.24180723057</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7902585286007935</v>
+        <v>0.7923287484187618</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4623.926656238262</v>
+        <v>4626.739604374264</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>942.1345468689595</v>
+        <v>943.0764247960906</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +743,7 @@
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>4426.86818233556</v>
+        <v>4430.623008398695</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.25613160044787</v>
+        <v>15.26907170125877</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.25613160044787</v>
+        <v>15.26907170125877</v>
       </c>
     </row>
     <row r="17">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.29185638673033</v>
+        <v>13.22932980424547</v>
       </c>
       <c r="F11" t="n">
-        <v>10.51015057339689</v>
+        <v>10.4607094887481</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.35239519926296</v>
+        <v>13.30295411461418</v>
       </c>
     </row>
     <row r="13">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.119462979747805</v>
+        <v>9.114843575886209</v>
       </c>
       <c r="C2" t="n">
-        <v>11.48385699579164</v>
+        <v>11.47866016644733</v>
       </c>
       <c r="D2" t="n">
-        <v>13.84825101183547</v>
+        <v>13.84247675700846</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2126450278793</v>
+        <v>16.20629334756959</v>
       </c>
       <c r="F2" t="n">
-        <v>18.57703904392312</v>
+        <v>18.57010993813071</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.537842813876271</v>
+        <v>9.533223410014674</v>
       </c>
       <c r="C3" t="n">
-        <v>11.90223682992011</v>
+        <v>11.8970400005758</v>
       </c>
       <c r="D3" t="n">
-        <v>14.26663084596393</v>
+        <v>14.26085659113693</v>
       </c>
       <c r="E3" t="n">
-        <v>16.63102486200777</v>
+        <v>16.62467318169805</v>
       </c>
       <c r="F3" t="n">
-        <v>18.99541887805159</v>
+        <v>18.98848977225918</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.956222648004736</v>
+        <v>9.95160324414314</v>
       </c>
       <c r="C4" t="n">
-        <v>12.32061666404858</v>
+        <v>12.31541983470427</v>
       </c>
       <c r="D4" t="n">
-        <v>14.6850106800924</v>
+        <v>14.67923642526539</v>
       </c>
       <c r="E4" t="n">
-        <v>17.04940469613623</v>
+        <v>17.04305301582652</v>
       </c>
       <c r="F4" t="n">
-        <v>19.41379871218005</v>
+        <v>19.40686960638764</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.3746024821332</v>
+        <v>10.3699830782716</v>
       </c>
       <c r="C5" t="n">
-        <v>12.73899649817704</v>
+        <v>12.73379966883273</v>
       </c>
       <c r="D5" t="n">
-        <v>15.10339051422087</v>
+        <v>15.09761625939386</v>
       </c>
       <c r="E5" t="n">
-        <v>17.4677845302647</v>
+        <v>17.46143284995498</v>
       </c>
       <c r="F5" t="n">
-        <v>19.83217854630852</v>
+        <v>19.82524944051611</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.79298231626167</v>
+        <v>10.78836291240007</v>
       </c>
       <c r="C6" t="n">
-        <v>13.15737633230551</v>
+        <v>13.1521795029612</v>
       </c>
       <c r="D6" t="n">
-        <v>15.52177034834933</v>
+        <v>15.51599609352233</v>
       </c>
       <c r="E6" t="n">
-        <v>17.88616436439316</v>
+        <v>17.87981268408345</v>
       </c>
       <c r="F6" t="n">
-        <v>20.25055838043698</v>
+        <v>20.24362927464458</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>14.75</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>14.78</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14.79</v>
+        <v>14.78</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.67923642526539</v>
+        <v>14.93130839059966</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.26907170125877</v>
+        <v>15.39703101668973</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.30295411461418</v>
+        <v>14.23272445146455</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.501023710280085</v>
+        <v>1.47814722368358</v>
       </c>
     </row>
     <row r="12">
@@ -553,7 +553,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>late-cycle/peak</t>
+          <t>elevated</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38337.24180723057</v>
+        <v>36205.58496498821</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7923287484187618</v>
+        <v>0.7764658181069377</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>624.4260092509445</v>
+        <v>540.9510092509445</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1248.708969977394</v>
+        <v>1212.536469977394</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4626.739604374264</v>
+        <v>4746.183229374264</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>943.0764247960906</v>
+        <v>980.4102247960903</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +743,7 @@
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>4430.623008398695</v>
+        <v>4467.752933398695</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.26907170125877</v>
+        <v>15.39703101668973</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.26907170125877</v>
+        <v>15.39703101668973</v>
       </c>
     </row>
     <row r="17">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.22932980424547</v>
+        <v>14.40518106382098</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4607094887481</v>
+        <v>11.39047982559847</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.30295411461418</v>
+        <v>14.23272445146455</v>
       </c>
     </row>
     <row r="13">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.114843575886209</v>
+        <v>9.191506666955638</v>
       </c>
       <c r="C2" t="n">
-        <v>11.47866016644733</v>
+        <v>11.50356774993969</v>
       </c>
       <c r="D2" t="n">
-        <v>13.84247675700846</v>
+        <v>13.81562883292375</v>
       </c>
       <c r="E2" t="n">
-        <v>16.20629334756959</v>
+        <v>16.1276899159078</v>
       </c>
       <c r="F2" t="n">
-        <v>18.57010993813071</v>
+        <v>18.43975099889186</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.533223410014674</v>
+        <v>9.749346445793593</v>
       </c>
       <c r="C3" t="n">
-        <v>11.8970400005758</v>
+        <v>12.06140752877765</v>
       </c>
       <c r="D3" t="n">
-        <v>14.26085659113693</v>
+        <v>14.37346861176171</v>
       </c>
       <c r="E3" t="n">
-        <v>16.62467318169805</v>
+        <v>16.68552969474576</v>
       </c>
       <c r="F3" t="n">
-        <v>18.98848977225918</v>
+        <v>18.99759077772981</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.95160324414314</v>
+        <v>10.30718622463155</v>
       </c>
       <c r="C4" t="n">
-        <v>12.31541983470427</v>
+        <v>12.6192473076156</v>
       </c>
       <c r="D4" t="n">
-        <v>14.67923642526539</v>
+        <v>14.93130839059966</v>
       </c>
       <c r="E4" t="n">
-        <v>17.04305301582652</v>
+        <v>17.24336947358371</v>
       </c>
       <c r="F4" t="n">
-        <v>19.40686960638764</v>
+        <v>19.55543055656777</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.3699830782716</v>
+        <v>10.8650260034695</v>
       </c>
       <c r="C5" t="n">
-        <v>12.73379966883273</v>
+        <v>13.17708708645355</v>
       </c>
       <c r="D5" t="n">
-        <v>15.09761625939386</v>
+        <v>15.48914816943761</v>
       </c>
       <c r="E5" t="n">
-        <v>17.46143284995498</v>
+        <v>17.80120925242166</v>
       </c>
       <c r="F5" t="n">
-        <v>19.82524944051611</v>
+        <v>20.11327033540572</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.78836291240007</v>
+        <v>11.42286578230745</v>
       </c>
       <c r="C6" t="n">
-        <v>13.1521795029612</v>
+        <v>13.73492686529151</v>
       </c>
       <c r="D6" t="n">
-        <v>15.51599609352233</v>
+        <v>16.04698794827556</v>
       </c>
       <c r="E6" t="n">
-        <v>17.87981268408345</v>
+        <v>18.35904903125962</v>
       </c>
       <c r="F6" t="n">
-        <v>20.24362927464458</v>
+        <v>20.67111011424367</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>14.74</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>14.77</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14.78</v>
+        <v>15.07</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.1</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.93130839059966</v>
+        <v>15.26365690567999</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.39703101668973</v>
+        <v>15.86977926497469</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.23272445146455</v>
+        <v>14.35447336673793</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.47814722368358</v>
+        <v>1.497000871009924</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36205.58496498821</v>
+        <v>32749.33223360152</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7764658181069377</v>
+        <v>0.6817212708963627</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>540.9510092509445</v>
+        <v>624.4260092509445</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1212.536469977394</v>
+        <v>1266.238719977394</v>
       </c>
     </row>
     <row r="4">
@@ -743,7 +743,7 @@
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>4467.752933398695</v>
+        <v>4604.930183398695</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.39703101668973</v>
+        <v>15.86977926497469</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.39703101668973</v>
+        <v>15.86977926497469</v>
       </c>
     </row>
     <row r="17">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.40518106382098</v>
+        <v>14.55915308218103</v>
       </c>
       <c r="F11" t="n">
-        <v>11.39047982559847</v>
+        <v>11.51222874087186</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.23272445146455</v>
+        <v>14.35447336673793</v>
       </c>
     </row>
     <row r="13">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.191506666955638</v>
+        <v>9.4573854790199</v>
       </c>
       <c r="C2" t="n">
-        <v>11.50356774993969</v>
+        <v>11.80268141351199</v>
       </c>
       <c r="D2" t="n">
-        <v>13.81562883292375</v>
+        <v>14.14797734800408</v>
       </c>
       <c r="E2" t="n">
-        <v>16.1276899159078</v>
+        <v>16.49327328249617</v>
       </c>
       <c r="F2" t="n">
-        <v>18.43975099889186</v>
+        <v>18.83856921698825</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.749346445793593</v>
+        <v>10.01522525785785</v>
       </c>
       <c r="C3" t="n">
-        <v>12.06140752877765</v>
+        <v>12.36052119234994</v>
       </c>
       <c r="D3" t="n">
-        <v>14.37346861176171</v>
+        <v>14.70581712684203</v>
       </c>
       <c r="E3" t="n">
-        <v>16.68552969474576</v>
+        <v>17.05111306133412</v>
       </c>
       <c r="F3" t="n">
-        <v>18.99759077772981</v>
+        <v>19.39640899582621</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.30718622463155</v>
+        <v>10.57306503669581</v>
       </c>
       <c r="C4" t="n">
-        <v>12.6192473076156</v>
+        <v>12.91836097118789</v>
       </c>
       <c r="D4" t="n">
-        <v>14.93130839059966</v>
+        <v>15.26365690567999</v>
       </c>
       <c r="E4" t="n">
-        <v>17.24336947358371</v>
+        <v>17.60895284017207</v>
       </c>
       <c r="F4" t="n">
-        <v>19.55543055656777</v>
+        <v>19.95424877466416</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.8650260034695</v>
+        <v>11.13090481553376</v>
       </c>
       <c r="C5" t="n">
-        <v>13.17708708645355</v>
+        <v>13.47620075002585</v>
       </c>
       <c r="D5" t="n">
-        <v>15.48914816943761</v>
+        <v>15.82149668451794</v>
       </c>
       <c r="E5" t="n">
-        <v>17.80120925242166</v>
+        <v>18.16679261901002</v>
       </c>
       <c r="F5" t="n">
-        <v>20.11327033540572</v>
+        <v>20.51208855350211</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.42286578230745</v>
+        <v>11.68874459437172</v>
       </c>
       <c r="C6" t="n">
-        <v>13.73492686529151</v>
+        <v>14.0340405288638</v>
       </c>
       <c r="D6" t="n">
-        <v>16.04698794827556</v>
+        <v>16.37933646335589</v>
       </c>
       <c r="E6" t="n">
-        <v>18.35904903125962</v>
+        <v>18.72463239784798</v>
       </c>
       <c r="F6" t="n">
-        <v>20.67111011424367</v>
+        <v>21.06992833234007</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.01</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.06</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.07</v>
+        <v>15.4</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.08</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32749.33223360152</v>
+        <v>31586.76014363639</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6817212708963627</v>
+        <v>0.6575207737067896</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.99</v>
+        <v>14.05</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31586.76014363639</v>
+        <v>32361.80820361313</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6575207737067896</v>
+        <v>0.6736544384998382</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32361.80820361313</v>
+        <v>32361.80820361314</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.26365690567999</v>
+        <v>15.18997020910227</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.35447336673793</v>
+        <v>13.60374907873331</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27000</v>
+        <v>33100</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29537.5</v>
+        <v>31037.5</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.497000871009924</v>
+        <v>1.663446935185219</v>
       </c>
     </row>
     <row r="12">
@@ -553,7 +553,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32361.80820361314</v>
+        <v>29270.42649721708</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6736544384998382</v>
+        <v>0.5995923328102031</v>
       </c>
     </row>
   </sheetData>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31200</v>
+        <v>32500</v>
       </c>
       <c r="C2" t="n">
-        <v>31200</v>
+        <v>32500</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9538566959571864</v>
+        <v>0.9672209934798549</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4769283479785932</v>
+        <v>0.4836104967399275</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4646462028442978</v>
+        <v>0.4711562688991972</v>
       </c>
     </row>
     <row r="3">
@@ -869,19 +869,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31450</v>
+        <v>33650</v>
       </c>
       <c r="C3" t="n">
-        <v>31450</v>
+        <v>33650</v>
       </c>
       <c r="D3" t="n">
-        <v>1.074814914213203</v>
+        <v>1.112189644573208</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5374074571066016</v>
+        <v>0.5560948222866042</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5100845848897492</v>
+        <v>0.5278218469698954</v>
       </c>
     </row>
     <row r="4">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28500</v>
+        <v>29500</v>
       </c>
       <c r="C4" t="n">
-        <v>28500</v>
+        <v>29500</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9279586504754049</v>
+        <v>0.9469857859314076</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4639793252377025</v>
+        <v>0.4734928929657038</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4290485068270166</v>
+        <v>0.4378458428423778</v>
       </c>
     </row>
     <row r="5">
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="C5" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7185091514478202</v>
+        <v>0.7479559087011576</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3592545757239101</v>
+        <v>0.3739779543505788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3236527709224415</v>
+        <v>0.3369170759915124</v>
       </c>
     </row>
     <row r="6">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25500</v>
+        <v>27500</v>
       </c>
       <c r="C6" t="n">
-        <v>25500</v>
+        <v>27500</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6256386093411406</v>
+        <v>0.6673170965304797</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3128193046705703</v>
+        <v>0.3336585482652398</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2745616163424083</v>
+        <v>0.2928522279487831</v>
       </c>
     </row>
     <row r="7">
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25000</v>
+        <v>26500</v>
       </c>
       <c r="C7" t="n">
-        <v>25000</v>
+        <v>26500</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7248515299331544</v>
+        <v>0.7533922331171584</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3624257649665772</v>
+        <v>0.3766961165585792</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3099092907069753</v>
+        <v>0.3221118297301718</v>
       </c>
     </row>
     <row r="8">
@@ -979,19 +979,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24500</v>
+        <v>26000</v>
       </c>
       <c r="C8" t="n">
-        <v>24500</v>
+        <v>26000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7376872959153784</v>
+        <v>0.7680401072380493</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3688436479576892</v>
+        <v>0.3840200536190246</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3072749069129764</v>
+        <v>0.3199180110105569</v>
       </c>
     </row>
     <row r="9">
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24000</v>
+        <v>25500</v>
       </c>
       <c r="C9" t="n">
-        <v>24000</v>
+        <v>25500</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5496810765286855</v>
+        <v>0.5800338878513565</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2748405382643427</v>
+        <v>0.2900169439256782</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2230667464202116</v>
+        <v>0.2353842577109636</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.842244625866077</v>
+        <v>2.944007361103458</v>
       </c>
     </row>
     <row r="11">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.55915308218103</v>
+        <v>13.48103959509502</v>
       </c>
       <c r="F11" t="n">
-        <v>11.51222874087186</v>
+        <v>10.65974171762985</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.35447336673793</v>
+        <v>13.60374907873331</v>
       </c>
     </row>
     <row r="13">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29537.5</v>
+        <v>31037.5</v>
       </c>
     </row>
   </sheetData>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.4573854790199</v>
+        <v>9.51764809966004</v>
       </c>
       <c r="C2" t="n">
-        <v>11.80268141351199</v>
+        <v>11.92675556530917</v>
       </c>
       <c r="D2" t="n">
-        <v>14.14797734800408</v>
+        <v>14.33586303095832</v>
       </c>
       <c r="E2" t="n">
-        <v>16.49327328249617</v>
+        <v>16.74497049660745</v>
       </c>
       <c r="F2" t="n">
-        <v>18.83856921698825</v>
+        <v>19.15407796225659</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.01522525785785</v>
+        <v>9.944701688732017</v>
       </c>
       <c r="C3" t="n">
-        <v>12.36052119234994</v>
+        <v>12.35380915438115</v>
       </c>
       <c r="D3" t="n">
-        <v>14.70581712684203</v>
+        <v>14.7629166200303</v>
       </c>
       <c r="E3" t="n">
-        <v>17.05111306133412</v>
+        <v>17.17202408567943</v>
       </c>
       <c r="F3" t="n">
-        <v>19.39640899582621</v>
+        <v>19.58113155132857</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.57306503669581</v>
+        <v>10.371755277804</v>
       </c>
       <c r="C4" t="n">
-        <v>12.91836097118789</v>
+        <v>12.78086274345313</v>
       </c>
       <c r="D4" t="n">
-        <v>15.26365690567999</v>
+        <v>15.18997020910227</v>
       </c>
       <c r="E4" t="n">
-        <v>17.60895284017207</v>
+        <v>17.59907767475141</v>
       </c>
       <c r="F4" t="n">
-        <v>19.95424877466416</v>
+        <v>20.00818514040055</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.13090481553376</v>
+        <v>10.79880886687597</v>
       </c>
       <c r="C5" t="n">
-        <v>13.47620075002585</v>
+        <v>13.20791633252511</v>
       </c>
       <c r="D5" t="n">
-        <v>15.82149668451794</v>
+        <v>15.61702379817425</v>
       </c>
       <c r="E5" t="n">
-        <v>18.16679261901002</v>
+        <v>18.02613126382339</v>
       </c>
       <c r="F5" t="n">
-        <v>20.51208855350211</v>
+        <v>20.43523872947253</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.68874459437172</v>
+        <v>11.22586245594795</v>
       </c>
       <c r="C6" t="n">
-        <v>14.0340405288638</v>
+        <v>13.63496992159709</v>
       </c>
       <c r="D6" t="n">
-        <v>16.37933646335589</v>
+        <v>16.04407738724623</v>
       </c>
       <c r="E6" t="n">
-        <v>18.72463239784798</v>
+        <v>18.45318485289537</v>
       </c>
       <c r="F6" t="n">
-        <v>21.06992833234007</v>
+        <v>20.8622923185445</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.35</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.39</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1304,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.05</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29270.42649721708</v>
+        <v>38015.26994050568</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5995923328102031</v>
+        <v>0.7787267598647574</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38015.26994050568</v>
+        <v>38015.26994050569</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.18997020910227</v>
+        <v>15.18893258823208</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.60374907873331</v>
+        <v>13.60029034249934</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.663446935185219</v>
+        <v>1.663845334050124</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38015.26994050569</v>
+        <v>38025.94880520753</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7787267598647574</v>
+        <v>0.7790106765991529</v>
       </c>
     </row>
   </sheetData>
@@ -853,13 +853,13 @@
         <v>32500</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9672209934798549</v>
+        <v>0.9678250295260772</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4836104967399275</v>
+        <v>0.4839125147630386</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4711562688991972</v>
+        <v>0.471450509172865</v>
       </c>
     </row>
     <row r="3">
@@ -897,13 +897,13 @@
         <v>29500</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9469857859314076</v>
+        <v>0.9463817498851853</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4734928929657038</v>
+        <v>0.4731908749425927</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4378458428423778</v>
+        <v>0.4375665623339537</v>
       </c>
     </row>
     <row r="5">
@@ -919,13 +919,13 @@
         <v>28500</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7479559087011576</v>
+        <v>0.7473518726549353</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3739779543505788</v>
+        <v>0.3736759363274677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3369170759915124</v>
+        <v>0.3366449876824033</v>
       </c>
     </row>
     <row r="6">
@@ -941,13 +941,13 @@
         <v>27500</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6673170965304797</v>
+        <v>0.6667130604842574</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3336585482652398</v>
+        <v>0.3333565302421287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2928522279487831</v>
+        <v>0.2925871466211545</v>
       </c>
     </row>
     <row r="7">
@@ -963,13 +963,13 @@
         <v>26500</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7533922331171584</v>
+        <v>0.7521841610247137</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3766961165585792</v>
+        <v>0.3760920805123569</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3221118297301718</v>
+        <v>0.3215953201418884</v>
       </c>
     </row>
     <row r="8">
@@ -985,13 +985,13 @@
         <v>26000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7680401072380493</v>
+        <v>0.7668320351456047</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3840200536190246</v>
+        <v>0.3834160175728024</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3199180110105569</v>
+        <v>0.3194148028872701</v>
       </c>
     </row>
     <row r="9">
@@ -1007,13 +1007,13 @@
         <v>25500</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5800338878513565</v>
+        <v>0.5794298518051341</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2900169439256782</v>
+        <v>0.289714925902567</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2353842577109636</v>
+        <v>0.2351391331081625</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.944007361103458</v>
+        <v>2.942220308917593</v>
       </c>
     </row>
     <row r="11">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.48103959509502</v>
+        <v>13.47892546893324</v>
       </c>
       <c r="F11" t="n">
-        <v>10.65974171762985</v>
+        <v>10.65807003358175</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.60374907873331</v>
+        <v>13.60029034249934</v>
       </c>
     </row>
     <row r="13">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.51764809966004</v>
+        <v>9.516921765050904</v>
       </c>
       <c r="C2" t="n">
-        <v>11.92675556530917</v>
+        <v>11.92602923070004</v>
       </c>
       <c r="D2" t="n">
-        <v>14.33586303095832</v>
+        <v>14.33513669634918</v>
       </c>
       <c r="E2" t="n">
-        <v>16.74497049660745</v>
+        <v>16.74424416199832</v>
       </c>
       <c r="F2" t="n">
-        <v>19.15407796225659</v>
+        <v>19.15335162764746</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.944701688732017</v>
+        <v>9.943819710992354</v>
       </c>
       <c r="C3" t="n">
-        <v>12.35380915438115</v>
+        <v>12.35292717664149</v>
       </c>
       <c r="D3" t="n">
-        <v>14.7629166200303</v>
+        <v>14.76203464229063</v>
       </c>
       <c r="E3" t="n">
-        <v>17.17202408567943</v>
+        <v>17.17114210793977</v>
       </c>
       <c r="F3" t="n">
-        <v>19.58113155132857</v>
+        <v>19.58024957358891</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.371755277804</v>
+        <v>10.3707176569338</v>
       </c>
       <c r="C4" t="n">
-        <v>12.78086274345313</v>
+        <v>12.77982512258294</v>
       </c>
       <c r="D4" t="n">
-        <v>15.18997020910227</v>
+        <v>15.18893258823208</v>
       </c>
       <c r="E4" t="n">
-        <v>17.59907767475141</v>
+        <v>17.59804005388122</v>
       </c>
       <c r="F4" t="n">
-        <v>20.00818514040055</v>
+        <v>20.00714751953036</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.79880886687597</v>
+        <v>10.79761560287525</v>
       </c>
       <c r="C5" t="n">
-        <v>13.20791633252511</v>
+        <v>13.20672306852439</v>
       </c>
       <c r="D5" t="n">
-        <v>15.61702379817425</v>
+        <v>15.61583053417353</v>
       </c>
       <c r="E5" t="n">
-        <v>18.02613126382339</v>
+        <v>18.02493799982267</v>
       </c>
       <c r="F5" t="n">
-        <v>20.43523872947253</v>
+        <v>20.4340454654718</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.22586245594795</v>
+        <v>11.2245135488167</v>
       </c>
       <c r="C6" t="n">
-        <v>13.63496992159709</v>
+        <v>13.63362101446584</v>
       </c>
       <c r="D6" t="n">
-        <v>16.04407738724623</v>
+        <v>16.04272848011498</v>
       </c>
       <c r="E6" t="n">
-        <v>18.45318485289537</v>
+        <v>18.45183594576412</v>
       </c>
       <c r="F6" t="n">
-        <v>20.8622923185445</v>
+        <v>20.86094341141326</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38025.94880520753</v>
+        <v>38025.94880520754</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.56</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>38025.94880520754</v>
+        <v>44372.02916555987</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7790106765991529</v>
+        <v>0.909018329546754</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.93</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44372.02916555987</v>
+        <v>55349.03303211532</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.909018329546754</v>
+        <v>1.133896431942606</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.18893258823208</v>
+        <v>15.24686446801159</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.60029034249934</v>
+        <v>13.79339660843105</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33100</v>
+        <v>35300</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31037.5</v>
+        <v>32450</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.663845334050124</v>
+        <v>1.729852435412692</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55349.03303211532</v>
+        <v>55288.6477159897</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.133896431942606</v>
+        <v>1.111275701064875</v>
       </c>
     </row>
   </sheetData>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32500</v>
+        <v>35400</v>
       </c>
       <c r="C2" t="n">
-        <v>32500</v>
+        <v>35400</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9678250295260772</v>
+        <v>1.039856328038087</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4839125147630386</v>
+        <v>0.5199281640190436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.471450509172865</v>
+        <v>0.5065386618077465</v>
       </c>
     </row>
     <row r="3">
@@ -869,19 +869,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33650</v>
+        <v>35200</v>
       </c>
       <c r="C3" t="n">
-        <v>33650</v>
+        <v>35200</v>
       </c>
       <c r="D3" t="n">
-        <v>1.112189644573208</v>
+        <v>1.157492348039882</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5560948222866042</v>
+        <v>0.5787461740199408</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5278218469698954</v>
+        <v>0.549321558582194</v>
       </c>
     </row>
     <row r="4">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29500</v>
+        <v>30100</v>
       </c>
       <c r="C4" t="n">
-        <v>29500</v>
+        <v>30100</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9463817498851853</v>
+        <v>0.9645028312718545</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4731908749425927</v>
+        <v>0.4822514156359273</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4375665623339537</v>
+        <v>0.4459449775866787</v>
       </c>
     </row>
     <row r="5">
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28500</v>
+        <v>29100</v>
       </c>
       <c r="C5" t="n">
-        <v>28500</v>
+        <v>29100</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7473518726549353</v>
+        <v>0.7654729540416045</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3736759363274677</v>
+        <v>0.3827364770208023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3366449876824033</v>
+        <v>0.3448076369556777</v>
       </c>
     </row>
     <row r="6">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27500</v>
+        <v>28100</v>
       </c>
       <c r="C6" t="n">
-        <v>27500</v>
+        <v>28100</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6667130604842574</v>
+        <v>0.6848341418709266</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3333565302421287</v>
+        <v>0.3424170709354633</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2925871466211545</v>
+        <v>0.3005395864500132</v>
       </c>
     </row>
     <row r="7">
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26500</v>
+        <v>27100</v>
       </c>
       <c r="C7" t="n">
-        <v>26500</v>
+        <v>27100</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7521841610247137</v>
+        <v>0.770305242411383</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3760920805123569</v>
+        <v>0.3851526212056915</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3215953201418884</v>
+        <v>0.3293429639661401</v>
       </c>
     </row>
     <row r="8">
@@ -979,19 +979,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26000</v>
+        <v>26600</v>
       </c>
       <c r="C8" t="n">
-        <v>26000</v>
+        <v>26600</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7668320351456047</v>
+        <v>0.784953116532274</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3834160175728024</v>
+        <v>0.392476558266137</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3194148028872701</v>
+        <v>0.326962924736572</v>
       </c>
     </row>
     <row r="9">
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25500</v>
+        <v>26100</v>
       </c>
       <c r="C9" t="n">
-        <v>25500</v>
+        <v>26100</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5794298518051341</v>
+        <v>0.5975509331918033</v>
       </c>
       <c r="E9" t="n">
-        <v>0.289714925902567</v>
+        <v>0.2987754665959017</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2351391331081625</v>
+        <v>0.2424928711921935</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.942220308917593</v>
+        <v>3.045951181277216</v>
       </c>
     </row>
     <row r="11">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.47892546893324</v>
+        <v>13.59195571408259</v>
       </c>
       <c r="F11" t="n">
-        <v>10.65807003358175</v>
+        <v>10.74744542715383</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.60029034249934</v>
+        <v>13.79339660843105</v>
       </c>
     </row>
     <row r="13">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31037.5</v>
+        <v>32450</v>
       </c>
     </row>
   </sheetData>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.516921765050904</v>
+        <v>9.557474080896561</v>
       </c>
       <c r="C2" t="n">
-        <v>11.92602923070004</v>
+        <v>11.9665815465457</v>
       </c>
       <c r="D2" t="n">
-        <v>14.33513669634918</v>
+        <v>14.37568901219484</v>
       </c>
       <c r="E2" t="n">
-        <v>16.74424416199832</v>
+        <v>16.78479647784398</v>
       </c>
       <c r="F2" t="n">
-        <v>19.15335162764746</v>
+        <v>19.19390394349311</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.943819710992354</v>
+        <v>9.993061808804939</v>
       </c>
       <c r="C3" t="n">
-        <v>12.35292717664149</v>
+        <v>12.40216927445407</v>
       </c>
       <c r="D3" t="n">
-        <v>14.76203464229063</v>
+        <v>14.81127674010322</v>
       </c>
       <c r="E3" t="n">
-        <v>17.17114210793977</v>
+        <v>17.22038420575235</v>
       </c>
       <c r="F3" t="n">
-        <v>19.58024957358891</v>
+        <v>19.62949167140149</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.3707176569338</v>
+        <v>10.42864953671332</v>
       </c>
       <c r="C4" t="n">
-        <v>12.77982512258294</v>
+        <v>12.83775700236245</v>
       </c>
       <c r="D4" t="n">
-        <v>15.18893258823208</v>
+        <v>15.24686446801159</v>
       </c>
       <c r="E4" t="n">
-        <v>17.59804005388122</v>
+        <v>17.65597193366073</v>
       </c>
       <c r="F4" t="n">
-        <v>20.00714751953036</v>
+        <v>20.06507939930987</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.79761560287525</v>
+        <v>10.86423726462169</v>
       </c>
       <c r="C5" t="n">
-        <v>13.20672306852439</v>
+        <v>13.27334473027083</v>
       </c>
       <c r="D5" t="n">
-        <v>15.61583053417353</v>
+        <v>15.68245219591997</v>
       </c>
       <c r="E5" t="n">
-        <v>18.02493799982267</v>
+        <v>18.09155966156911</v>
       </c>
       <c r="F5" t="n">
-        <v>20.4340454654718</v>
+        <v>20.50066712721824</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.2245135488167</v>
+        <v>11.29982499253007</v>
       </c>
       <c r="C6" t="n">
-        <v>13.63362101446584</v>
+        <v>13.7089324581792</v>
       </c>
       <c r="D6" t="n">
-        <v>16.04272848011498</v>
+        <v>16.11803992382835</v>
       </c>
       <c r="E6" t="n">
-        <v>18.45183594576412</v>
+        <v>18.52714738947748</v>
       </c>
       <c r="F6" t="n">
-        <v>20.86094341141326</v>
+        <v>20.93625485512662</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.25</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.29</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.3</v>
+        <v>15.36</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.57</v>
+        <v>15.44</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>55288.6477159897</v>
+        <v>53061.37639326917</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.111275701064875</v>
+        <v>1.066508599627845</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.44</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53061.37639326917</v>
+        <v>58886.54754499982</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.066508599627845</v>
+        <v>1.183591788001617</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58886.54754499982</v>
+        <v>58886.54754499981</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58886.54754499981</v>
+        <v>58886.54754499982</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.78</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58886.54754499982</v>
+        <v>44837.6053555318</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.183591788001617</v>
+        <v>0.901214686629578</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.24686446801159</v>
+        <v>15.48275197220072</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.86977926497469</v>
+        <v>16.12123123873832</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.79339660843105</v>
+        <v>13.99296701694633</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.729852435412692</v>
+        <v>1.728587183805877</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>44837.6053555318</v>
+        <v>40715.36011153575</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.901214686629578</v>
+        <v>0.8199839187237119</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>624.4260092509445</v>
+        <v>621.3353872439189</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1266.238719977394</v>
+        <v>1282.234081828126</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4746.183229374264</v>
+        <v>4807.453565374663</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>980.4102247960903</v>
+        <v>979.198910093572</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +743,7 @@
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>4604.930183398695</v>
+        <v>4677.893944540281</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15.86977926497469</v>
+        <v>16.12123123873832</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15.86977926497469</v>
+        <v>16.12123123873832</v>
       </c>
     </row>
     <row r="17">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.59195571408259</v>
+        <v>13.84434612376337</v>
       </c>
       <c r="F11" t="n">
-        <v>10.74744542715383</v>
+        <v>10.94701583566911</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.79339660843105</v>
+        <v>13.99296701694633</v>
       </c>
     </row>
     <row r="13">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.557474080896561</v>
+        <v>9.746184084247863</v>
       </c>
       <c r="C2" t="n">
-        <v>11.9665815465457</v>
+        <v>12.17888030031591</v>
       </c>
       <c r="D2" t="n">
-        <v>14.37568901219484</v>
+        <v>14.61157651638397</v>
       </c>
       <c r="E2" t="n">
-        <v>16.78479647784398</v>
+        <v>17.04427273245201</v>
       </c>
       <c r="F2" t="n">
-        <v>19.19390394349311</v>
+        <v>19.47696894852006</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.993061808804939</v>
+        <v>10.18177181215624</v>
       </c>
       <c r="C3" t="n">
-        <v>12.40216927445407</v>
+        <v>12.61446802822429</v>
       </c>
       <c r="D3" t="n">
-        <v>14.81127674010322</v>
+        <v>15.04716424429234</v>
       </c>
       <c r="E3" t="n">
-        <v>17.22038420575235</v>
+        <v>17.47986046036039</v>
       </c>
       <c r="F3" t="n">
-        <v>19.62949167140149</v>
+        <v>19.91255667642844</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.42864953671332</v>
+        <v>10.61735954006462</v>
       </c>
       <c r="C4" t="n">
-        <v>12.83775700236245</v>
+        <v>13.05005575613266</v>
       </c>
       <c r="D4" t="n">
-        <v>15.24686446801159</v>
+        <v>15.48275197220072</v>
       </c>
       <c r="E4" t="n">
-        <v>17.65597193366073</v>
+        <v>17.91544818826877</v>
       </c>
       <c r="F4" t="n">
-        <v>20.06507939930987</v>
+        <v>20.34814440433682</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.86423726462169</v>
+        <v>11.05294726797299</v>
       </c>
       <c r="C5" t="n">
-        <v>13.27334473027083</v>
+        <v>13.48564348404104</v>
       </c>
       <c r="D5" t="n">
-        <v>15.68245219591997</v>
+        <v>15.9183397001091</v>
       </c>
       <c r="E5" t="n">
-        <v>18.09155966156911</v>
+        <v>18.35103591617714</v>
       </c>
       <c r="F5" t="n">
-        <v>20.50066712721824</v>
+        <v>20.78373213224519</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.29982499253007</v>
+        <v>11.48853499588137</v>
       </c>
       <c r="C6" t="n">
-        <v>13.7089324581792</v>
+        <v>13.92123121194942</v>
       </c>
       <c r="D6" t="n">
-        <v>16.11803992382835</v>
+        <v>16.35392742801747</v>
       </c>
       <c r="E6" t="n">
-        <v>18.52714738947748</v>
+        <v>18.78662364408552</v>
       </c>
       <c r="F6" t="n">
-        <v>20.93625485512662</v>
+        <v>21.21931986015357</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.31</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.35</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.36</v>
+        <v>15.59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.96</v>
+        <v>15.08</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40715.36011153575</v>
+        <v>42767.22998309504</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8199839187237119</v>
+        <v>0.8613073969732783</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.48275197220072</v>
+        <v>15.50365910053079</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.99296701694633</v>
+        <v>14.06265744471322</v>
       </c>
     </row>
     <row r="9">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32450</v>
+        <v>32743.75</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.728587183805877</v>
+        <v>1.724963393983792</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42767.22998309504</v>
+        <v>42606.88977503307</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8613073969732783</v>
+        <v>0.8551506312370181</v>
       </c>
     </row>
   </sheetData>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35400</v>
+        <v>34900</v>
       </c>
       <c r="C2" t="n">
-        <v>35400</v>
+        <v>34900</v>
       </c>
       <c r="D2" t="n">
-        <v>1.039856328038087</v>
+        <v>1.023547354790085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5199281640190436</v>
+        <v>0.5117736773950425</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5065386618077465</v>
+        <v>0.4985941744187168</v>
       </c>
     </row>
     <row r="3">
@@ -869,19 +869,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35200</v>
+        <v>35725</v>
       </c>
       <c r="C3" t="n">
-        <v>35200</v>
+        <v>35725</v>
       </c>
       <c r="D3" t="n">
-        <v>1.157492348039882</v>
+        <v>1.168025226595883</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5787461740199408</v>
+        <v>0.5840126132979414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.549321558582194</v>
+        <v>0.5543202415320534</v>
       </c>
     </row>
     <row r="4">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30100</v>
+        <v>30675</v>
       </c>
       <c r="C4" t="n">
-        <v>30100</v>
+        <v>30675</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9645028312718545</v>
+        <v>0.9795659801745232</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4822514156359273</v>
+        <v>0.4897829900872616</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4459449775866787</v>
+        <v>0.4529095352655064</v>
       </c>
     </row>
     <row r="5">
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29100</v>
+        <v>29675</v>
       </c>
       <c r="C5" t="n">
-        <v>29100</v>
+        <v>29675</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7654729540416045</v>
+        <v>0.7805361029442733</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3827364770208023</v>
+        <v>0.3902680514721367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3448076369556777</v>
+        <v>0.3515928391640871</v>
       </c>
     </row>
     <row r="6">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28100</v>
+        <v>28675</v>
       </c>
       <c r="C6" t="n">
-        <v>28100</v>
+        <v>28675</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6848341418709266</v>
+        <v>0.6998972907735954</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3424170709354633</v>
+        <v>0.3499486453867977</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3005395864500132</v>
+        <v>0.307150052057752</v>
       </c>
     </row>
     <row r="7">
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27100</v>
+        <v>27675</v>
       </c>
       <c r="C7" t="n">
-        <v>27100</v>
+        <v>27675</v>
       </c>
       <c r="D7" t="n">
-        <v>0.770305242411383</v>
+        <v>0.7853683913140518</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3851526212056915</v>
+        <v>0.3926841956570259</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3293429639661401</v>
+        <v>0.3357831928950494</v>
       </c>
     </row>
     <row r="8">
@@ -979,19 +979,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26600</v>
+        <v>27175</v>
       </c>
       <c r="C8" t="n">
-        <v>26600</v>
+        <v>27175</v>
       </c>
       <c r="D8" t="n">
-        <v>0.784953116532274</v>
+        <v>0.8000162654349426</v>
       </c>
       <c r="E8" t="n">
-        <v>0.392476558266137</v>
+        <v>0.4000081327174713</v>
       </c>
       <c r="F8" t="n">
-        <v>0.326962924736572</v>
+        <v>0.3332373010238041</v>
       </c>
     </row>
     <row r="9">
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26100</v>
+        <v>26675</v>
       </c>
       <c r="C9" t="n">
-        <v>26100</v>
+        <v>26675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5975509331918033</v>
+        <v>0.6126140820944721</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2987754665959017</v>
+        <v>0.3063070410472361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2424928711921935</v>
+        <v>0.2486056659745443</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.045951181277216</v>
+        <v>3.082193002331513</v>
       </c>
     </row>
     <row r="11">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.84434612376337</v>
+        <v>13.88664752312537</v>
       </c>
       <c r="F11" t="n">
-        <v>10.94701583566911</v>
+        <v>10.98046444238171</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.99296701694633</v>
+        <v>14.06265744471322</v>
       </c>
     </row>
     <row r="13">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32450</v>
+        <v>32743.75</v>
       </c>
     </row>
   </sheetData>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.746184084247863</v>
+        <v>9.760819074078912</v>
       </c>
       <c r="C2" t="n">
-        <v>12.17888030031591</v>
+        <v>12.19351529014696</v>
       </c>
       <c r="D2" t="n">
-        <v>14.61157651638397</v>
+        <v>14.62621150621501</v>
       </c>
       <c r="E2" t="n">
-        <v>17.04427273245201</v>
+        <v>17.05890772228306</v>
       </c>
       <c r="F2" t="n">
-        <v>19.47696894852006</v>
+        <v>19.49160393835111</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.18177181215624</v>
+        <v>10.1995428712368</v>
       </c>
       <c r="C3" t="n">
-        <v>12.61446802822429</v>
+        <v>12.63223908730484</v>
       </c>
       <c r="D3" t="n">
-        <v>15.04716424429234</v>
+        <v>15.0649353033729</v>
       </c>
       <c r="E3" t="n">
-        <v>17.47986046036039</v>
+        <v>17.49763151944095</v>
       </c>
       <c r="F3" t="n">
-        <v>19.91255667642844</v>
+        <v>19.930327735509</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.61735954006462</v>
+        <v>10.63826666839469</v>
       </c>
       <c r="C4" t="n">
-        <v>13.05005575613266</v>
+        <v>13.07096288446273</v>
       </c>
       <c r="D4" t="n">
-        <v>15.48275197220072</v>
+        <v>15.50365910053079</v>
       </c>
       <c r="E4" t="n">
-        <v>17.91544818826877</v>
+        <v>17.93635531659883</v>
       </c>
       <c r="F4" t="n">
-        <v>20.34814440433682</v>
+        <v>20.36905153266689</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.05294726797299</v>
+        <v>11.07699046555257</v>
       </c>
       <c r="C5" t="n">
-        <v>13.48564348404104</v>
+        <v>13.50968668162062</v>
       </c>
       <c r="D5" t="n">
-        <v>15.9183397001091</v>
+        <v>15.94238289768868</v>
       </c>
       <c r="E5" t="n">
-        <v>18.35103591617714</v>
+        <v>18.37507911375672</v>
       </c>
       <c r="F5" t="n">
-        <v>20.78373213224519</v>
+        <v>20.80777532982477</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.48853499588137</v>
+        <v>11.51571426271046</v>
       </c>
       <c r="C6" t="n">
-        <v>13.92123121194942</v>
+        <v>13.94841047877851</v>
       </c>
       <c r="D6" t="n">
-        <v>16.35392742801747</v>
+        <v>16.38110669484657</v>
       </c>
       <c r="E6" t="n">
-        <v>18.78662364408552</v>
+        <v>18.81380291091461</v>
       </c>
       <c r="F6" t="n">
-        <v>21.21931986015357</v>
+        <v>21.24649912698266</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.55</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.58</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.59</v>
+        <v>15.62</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42606.88977503307</v>
+        <v>42606.88977503306</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.08</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42606.88977503306</v>
+        <v>53849.86399072054</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8551506312370181</v>
+        <v>1.080805133320871</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53849.86399072054</v>
+        <v>53849.86399072055</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.50365910053079</v>
+        <v>15.56928129621567</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.12123123873832</v>
+        <v>16.19071621668203</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.06265744471322</v>
+        <v>14.11926648179418</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.724963393983792</v>
+        <v>1.724460243059551</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53849.86399072055</v>
+        <v>52674.96387046848</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.080805133320871</v>
+        <v>1.058368854695231</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4807.453565374663</v>
+        <v>4821.81985586341</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>979.198910093572</v>
+        <v>984.9950596037218</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +743,7 @@
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>4677.893944540281</v>
+        <v>4698.056384539179</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.12123123873832</v>
+        <v>16.19071621668203</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.12123123873832</v>
+        <v>16.19071621668203</v>
       </c>
     </row>
     <row r="17">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.88664752312537</v>
+        <v>13.95823918927864</v>
       </c>
       <c r="F11" t="n">
-        <v>10.98046444238171</v>
+        <v>11.03707347946267</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.06265744471322</v>
+        <v>14.11926648179418</v>
       </c>
     </row>
     <row r="13">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.760819074078912</v>
+        <v>9.813316830626816</v>
       </c>
       <c r="C2" t="n">
-        <v>12.19351529014696</v>
+        <v>12.25257526626336</v>
       </c>
       <c r="D2" t="n">
-        <v>14.62621150621501</v>
+        <v>14.6918337018999</v>
       </c>
       <c r="E2" t="n">
-        <v>17.05890772228306</v>
+        <v>17.13109213753644</v>
       </c>
       <c r="F2" t="n">
-        <v>19.49160393835111</v>
+        <v>19.57035057317298</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.1995428712368</v>
+        <v>10.2520406277847</v>
       </c>
       <c r="C3" t="n">
-        <v>12.63223908730484</v>
+        <v>12.69129906342124</v>
       </c>
       <c r="D3" t="n">
-        <v>15.0649353033729</v>
+        <v>15.13055749905779</v>
       </c>
       <c r="E3" t="n">
-        <v>17.49763151944095</v>
+        <v>17.56981593469433</v>
       </c>
       <c r="F3" t="n">
-        <v>19.930327735509</v>
+        <v>20.00907437033086</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.63826666839469</v>
+        <v>10.69076442494259</v>
       </c>
       <c r="C4" t="n">
-        <v>13.07096288446273</v>
+        <v>13.13002286057913</v>
       </c>
       <c r="D4" t="n">
-        <v>15.50365910053079</v>
+        <v>15.56928129621567</v>
       </c>
       <c r="E4" t="n">
-        <v>17.93635531659883</v>
+        <v>18.00853973185221</v>
       </c>
       <c r="F4" t="n">
-        <v>20.36905153266689</v>
+        <v>20.44779816748875</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.07699046555257</v>
+        <v>11.12948822210048</v>
       </c>
       <c r="C5" t="n">
-        <v>13.50968668162062</v>
+        <v>13.56874665773702</v>
       </c>
       <c r="D5" t="n">
-        <v>15.94238289768868</v>
+        <v>16.00800509337356</v>
       </c>
       <c r="E5" t="n">
-        <v>18.37507911375672</v>
+        <v>18.4472635290101</v>
       </c>
       <c r="F5" t="n">
-        <v>20.80777532982477</v>
+        <v>20.88652196464664</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.51571426271046</v>
+        <v>11.56821201925836</v>
       </c>
       <c r="C6" t="n">
-        <v>13.94841047877851</v>
+        <v>14.0074704548949</v>
       </c>
       <c r="D6" t="n">
-        <v>16.38110669484657</v>
+        <v>16.44672889053145</v>
       </c>
       <c r="E6" t="n">
-        <v>18.81380291091461</v>
+        <v>18.88598732616799</v>
       </c>
       <c r="F6" t="n">
-        <v>21.24649912698266</v>
+        <v>21.32524576180452</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.57</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.6</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.62</v>
+        <v>15.68</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52674.96387046848</v>
+        <v>52674.96387046849</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52674.96387046849</v>
+        <v>52674.96387046848</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15.74</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52674.96387046849</v>
+        <v>59821.84490195637</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.058368854695231</v>
+        <v>1.201967174203137</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.16</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59821.84490195637</v>
+        <v>62033.97474503594</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.201967174203137</v>
+        <v>1.24641427309844</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.56928129621567</v>
+        <v>15.82577852027861</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.19071621668203</v>
+        <v>16.45740731010542</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.11926648179418</v>
+        <v>14.35197801068272</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.724460243059551</v>
+        <v>1.725220894400193</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62033.97474503594</v>
+        <v>57623.8770039451</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.24641427309844</v>
+        <v>1.158717677065392</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>621.3353872439189</v>
+        <v>635.463999733674</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4821.81985586341</v>
+        <v>4835.635990464123</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>984.9950596037218</v>
+        <v>1034.436005486279</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +743,7 @@
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>4698.056384539179</v>
+        <v>4775.442077512202</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.19071621668203</v>
+        <v>16.45740731010542</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.19071621668203</v>
+        <v>16.45740731010542</v>
       </c>
     </row>
     <row r="17">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.95823918927864</v>
+        <v>14.25254213003311</v>
       </c>
       <c r="F11" t="n">
-        <v>11.03707347946267</v>
+        <v>11.26978500835121</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.11926648179418</v>
+        <v>14.35197801068272</v>
       </c>
     </row>
     <row r="13">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.813316830626816</v>
+        <v>10.01851460987718</v>
       </c>
       <c r="C2" t="n">
-        <v>12.25257526626336</v>
+        <v>12.48342276792001</v>
       </c>
       <c r="D2" t="n">
-        <v>14.6918337018999</v>
+        <v>14.94833092596284</v>
       </c>
       <c r="E2" t="n">
-        <v>17.13109213753644</v>
+        <v>17.41323908400567</v>
       </c>
       <c r="F2" t="n">
-        <v>19.57035057317298</v>
+        <v>19.87814724204851</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.2520406277847</v>
+        <v>10.45723840703506</v>
       </c>
       <c r="C3" t="n">
-        <v>12.69129906342124</v>
+        <v>12.9221465650779</v>
       </c>
       <c r="D3" t="n">
-        <v>15.13055749905779</v>
+        <v>15.38705472312072</v>
       </c>
       <c r="E3" t="n">
-        <v>17.56981593469433</v>
+        <v>17.85196288116356</v>
       </c>
       <c r="F3" t="n">
-        <v>20.00907437033086</v>
+        <v>20.31687103920639</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.69076442494259</v>
+        <v>10.89596220419295</v>
       </c>
       <c r="C4" t="n">
-        <v>13.13002286057913</v>
+        <v>13.36087036223578</v>
       </c>
       <c r="D4" t="n">
-        <v>15.56928129621567</v>
+        <v>15.82577852027861</v>
       </c>
       <c r="E4" t="n">
-        <v>18.00853973185221</v>
+        <v>18.29068667832145</v>
       </c>
       <c r="F4" t="n">
-        <v>20.44779816748875</v>
+        <v>20.75559483636428</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.12948822210048</v>
+        <v>11.33468600135084</v>
       </c>
       <c r="C5" t="n">
-        <v>13.56874665773702</v>
+        <v>13.79959415939367</v>
       </c>
       <c r="D5" t="n">
-        <v>16.00800509337356</v>
+        <v>16.2645023174365</v>
       </c>
       <c r="E5" t="n">
-        <v>18.4472635290101</v>
+        <v>18.72941047547933</v>
       </c>
       <c r="F5" t="n">
-        <v>20.88652196464664</v>
+        <v>21.19431863352217</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.56821201925836</v>
+        <v>11.77340979850872</v>
       </c>
       <c r="C6" t="n">
-        <v>14.0074704548949</v>
+        <v>14.23831795655156</v>
       </c>
       <c r="D6" t="n">
-        <v>16.44672889053145</v>
+        <v>16.70322611459439</v>
       </c>
       <c r="E6" t="n">
-        <v>18.88598732616799</v>
+        <v>19.16813427263722</v>
       </c>
       <c r="F6" t="n">
-        <v>21.32524576180452</v>
+        <v>21.63304243068005</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.64</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.67</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.68</v>
+        <v>15.94</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.82577852027861</v>
+        <v>15.93305200682382</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.35197801068272</v>
+        <v>14.70955629916675</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35300</v>
+        <v>31550</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32743.75</v>
+        <v>33287.5</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.725220894400193</v>
+        <v>1.621509060171931</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57623.8770039451</v>
+        <v>56052.72786597301</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.158717677065392</v>
+        <v>1.117723074547096</v>
       </c>
     </row>
   </sheetData>
@@ -804,7 +804,7 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34900</v>
+        <v>38800</v>
       </c>
       <c r="C2" t="n">
-        <v>34900</v>
+        <v>38800</v>
       </c>
       <c r="D2" t="n">
-        <v>1.023547354790085</v>
+        <v>1.125327428578544</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5117736773950425</v>
+        <v>0.5626637142892718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4985941744187168</v>
+        <v>0.5481736605317359</v>
       </c>
     </row>
     <row r="3">
@@ -869,19 +869,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35725</v>
+        <v>37250</v>
       </c>
       <c r="C3" t="n">
-        <v>35725</v>
+        <v>37250</v>
       </c>
       <c r="D3" t="n">
-        <v>1.168025226595883</v>
+        <v>1.214573754407889</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5840126132979414</v>
+        <v>0.6072868772039447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5543202415320534</v>
+        <v>0.5764111952136901</v>
       </c>
     </row>
     <row r="4">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30675</v>
+        <v>25875</v>
       </c>
       <c r="C4" t="n">
-        <v>30675</v>
+        <v>25875</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9795659801745232</v>
+        <v>0.8623074827016181</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4897829900872616</v>
+        <v>0.431153741350809</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4529095352655064</v>
+        <v>0.3986942065676649</v>
       </c>
     </row>
     <row r="5">
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29675</v>
+        <v>31225</v>
       </c>
       <c r="C5" t="n">
-        <v>29675</v>
+        <v>31225</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7805361029442733</v>
+        <v>0.8208555090296122</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3902680514721367</v>
+        <v>0.4104277545148061</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3515928391640871</v>
+        <v>0.3697547337971226</v>
       </c>
     </row>
     <row r="6">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28675</v>
+        <v>31250</v>
       </c>
       <c r="C6" t="n">
-        <v>28675</v>
+        <v>31250</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6998972907735954</v>
+        <v>0.7687951522958272</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3499486453867977</v>
+        <v>0.3843975761479136</v>
       </c>
       <c r="F6" t="n">
-        <v>0.307150052057752</v>
+        <v>0.3373858909903916</v>
       </c>
     </row>
     <row r="7">
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27675</v>
+        <v>31250</v>
       </c>
       <c r="C7" t="n">
-        <v>27675</v>
+        <v>31250</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7853683913140518</v>
+        <v>0.882655947008732</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3926841956570259</v>
+        <v>0.441327973504366</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3357831928950494</v>
+        <v>0.3773783556765008</v>
       </c>
     </row>
     <row r="8">
@@ -979,19 +979,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27175</v>
+        <v>30750</v>
       </c>
       <c r="C8" t="n">
-        <v>27175</v>
+        <v>30750</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8000162654349426</v>
+        <v>0.8970018031065118</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4000081327174713</v>
+        <v>0.4485009015532559</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3332373010238041</v>
+        <v>0.3736354781714216</v>
       </c>
     </row>
     <row r="9">
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26675</v>
+        <v>30250</v>
       </c>
       <c r="C9" t="n">
-        <v>26675</v>
+        <v>30250</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6126140820944721</v>
+        <v>0.70929760174293</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3063070410472361</v>
+        <v>0.354648800871465</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2486056659745443</v>
+        <v>0.2878409227103846</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.082193002331513</v>
+        <v>3.269274443658913</v>
       </c>
     </row>
     <row r="11">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.25254213003311</v>
+        <v>14.46816412240803</v>
       </c>
       <c r="F11" t="n">
-        <v>11.26978500835121</v>
+        <v>11.44028185550784</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.35197801068272</v>
+        <v>14.70955629916675</v>
       </c>
     </row>
     <row r="13">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32743.75</v>
+        <v>33287.5</v>
       </c>
     </row>
   </sheetData>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.01851460987718</v>
+        <v>10.09360605045882</v>
       </c>
       <c r="C2" t="n">
-        <v>12.48342276792001</v>
+        <v>12.55851420850165</v>
       </c>
       <c r="D2" t="n">
-        <v>14.94833092596284</v>
+        <v>15.02342236654448</v>
       </c>
       <c r="E2" t="n">
-        <v>17.41323908400567</v>
+        <v>17.48833052458732</v>
       </c>
       <c r="F2" t="n">
-        <v>19.87814724204851</v>
+        <v>19.95323868263015</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.45723840703506</v>
+        <v>10.54842087059849</v>
       </c>
       <c r="C3" t="n">
-        <v>12.9221465650779</v>
+        <v>13.01332902864132</v>
       </c>
       <c r="D3" t="n">
-        <v>15.38705472312072</v>
+        <v>15.47823718668415</v>
       </c>
       <c r="E3" t="n">
-        <v>17.85196288116356</v>
+        <v>17.94314534472699</v>
       </c>
       <c r="F3" t="n">
-        <v>20.31687103920639</v>
+        <v>20.40805350276982</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.89596220419295</v>
+        <v>11.00323569073816</v>
       </c>
       <c r="C4" t="n">
-        <v>13.36087036223578</v>
+        <v>13.46814384878099</v>
       </c>
       <c r="D4" t="n">
-        <v>15.82577852027861</v>
+        <v>15.93305200682382</v>
       </c>
       <c r="E4" t="n">
-        <v>18.29068667832145</v>
+        <v>18.39796016486666</v>
       </c>
       <c r="F4" t="n">
-        <v>20.75559483636428</v>
+        <v>20.86286832290949</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.33468600135084</v>
+        <v>11.45805051087783</v>
       </c>
       <c r="C5" t="n">
-        <v>13.79959415939367</v>
+        <v>13.92295866892066</v>
       </c>
       <c r="D5" t="n">
-        <v>16.2645023174365</v>
+        <v>16.38786682696349</v>
       </c>
       <c r="E5" t="n">
-        <v>18.72941047547933</v>
+        <v>18.85277498500632</v>
       </c>
       <c r="F5" t="n">
-        <v>21.19431863352217</v>
+        <v>21.31768314304916</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.77340979850872</v>
+        <v>11.91286533101749</v>
       </c>
       <c r="C6" t="n">
-        <v>14.23831795655156</v>
+        <v>14.37777348906033</v>
       </c>
       <c r="D6" t="n">
-        <v>16.70322611459439</v>
+        <v>16.84268164710316</v>
       </c>
       <c r="E6" t="n">
-        <v>19.16813427263722</v>
+        <v>19.30758980514599</v>
       </c>
       <c r="F6" t="n">
-        <v>21.63304243068005</v>
+        <v>21.77249796318883</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.89</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.93</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.94</v>
+        <v>16.05</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.93305200682382</v>
+        <v>15.64756113114178</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.70955629916675</v>
+        <v>13.75792004689328</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.621509060171931</v>
+        <v>1.591674517581763</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56052.72786597301</v>
+        <v>61361.17710389959</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.117723074547096</v>
+        <v>1.233902648773563</v>
       </c>
     </row>
   </sheetData>
@@ -803,8 +803,8 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -853,13 +853,13 @@
         <v>38800</v>
       </c>
       <c r="D2" t="n">
-        <v>1.125327428578544</v>
+        <v>1.344894531380352</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5626637142892718</v>
+        <v>0.672447265690176</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5481736605317359</v>
+        <v>0.6551300000099703</v>
       </c>
     </row>
     <row r="3">
@@ -875,13 +875,13 @@
         <v>37250</v>
       </c>
       <c r="D3" t="n">
-        <v>1.214573754407889</v>
+        <v>1.306085215410569</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6072868772039447</v>
+        <v>0.6530426077052844</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5764111952136901</v>
+        <v>0.6198406126705333</v>
       </c>
     </row>
     <row r="4">
@@ -897,13 +897,13 @@
         <v>25875</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8623074827016181</v>
+        <v>0.6260085814194517</v>
       </c>
       <c r="E4" t="n">
-        <v>0.431153741350809</v>
+        <v>0.3130042907097259</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3986942065676649</v>
+        <v>0.2894396716721306</v>
       </c>
     </row>
     <row r="5">
@@ -919,13 +919,13 @@
         <v>31225</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8208555090296122</v>
+        <v>0.7536867006896918</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4104277545148061</v>
+        <v>0.3768433503448459</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3697547337971226</v>
+        <v>0.3394985138241854</v>
       </c>
     </row>
     <row r="6">
@@ -941,13 +941,13 @@
         <v>31250</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7687951522958272</v>
+        <v>0.5334023050829944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3843975761479136</v>
+        <v>0.2667011525414972</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3373858909903916</v>
+        <v>0.2340836976135177</v>
       </c>
     </row>
     <row r="7">
@@ -963,13 +963,13 @@
         <v>31250</v>
       </c>
       <c r="D7" t="n">
-        <v>0.882655947008732</v>
+        <v>0.5312881789212163</v>
       </c>
       <c r="E7" t="n">
-        <v>0.441327973504366</v>
+        <v>0.2656440894606081</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3773783556765008</v>
+        <v>0.2271515419242597</v>
       </c>
     </row>
     <row r="8">
@@ -985,13 +985,13 @@
         <v>30750</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8970018031065118</v>
+        <v>0.5142241606154362</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4485009015532559</v>
+        <v>0.2571120803077181</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3736354781714216</v>
+        <v>0.2141939843080028</v>
       </c>
     </row>
     <row r="9">
@@ -1007,13 +1007,13 @@
         <v>30250</v>
       </c>
       <c r="D9" t="n">
-        <v>0.70929760174293</v>
+        <v>0.4980661963789895</v>
       </c>
       <c r="E9" t="n">
-        <v>0.354648800871465</v>
+        <v>0.2490330981894947</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2878409227103846</v>
+        <v>0.2021208491108633</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.269274443658913</v>
+        <v>2.781458871133463</v>
       </c>
     </row>
     <row r="11">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.46816412240803</v>
+        <v>13.88158471792154</v>
       </c>
       <c r="F11" t="n">
-        <v>11.44028185550784</v>
+        <v>10.97646117575982</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.70955629916675</v>
+        <v>13.75792004689328</v>
       </c>
     </row>
     <row r="13">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.09360605045882</v>
+        <v>9.893762437481392</v>
       </c>
       <c r="C2" t="n">
-        <v>12.55851420850165</v>
+        <v>12.35867059552423</v>
       </c>
       <c r="D2" t="n">
-        <v>15.02342236654448</v>
+        <v>14.82357875356705</v>
       </c>
       <c r="E2" t="n">
-        <v>17.48833052458732</v>
+        <v>17.28848691160989</v>
       </c>
       <c r="F2" t="n">
-        <v>19.95323868263015</v>
+        <v>19.75339506965272</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.54842087059849</v>
+        <v>10.30575362626875</v>
       </c>
       <c r="C3" t="n">
-        <v>13.01332902864132</v>
+        <v>12.77066178431159</v>
       </c>
       <c r="D3" t="n">
-        <v>15.47823718668415</v>
+        <v>15.23556994235441</v>
       </c>
       <c r="E3" t="n">
-        <v>17.94314534472699</v>
+        <v>17.70047810039725</v>
       </c>
       <c r="F3" t="n">
-        <v>20.40805350276982</v>
+        <v>20.16538625844008</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.00323569073816</v>
+        <v>10.71774481505611</v>
       </c>
       <c r="C4" t="n">
-        <v>13.46814384878099</v>
+        <v>13.18265297309895</v>
       </c>
       <c r="D4" t="n">
-        <v>15.93305200682382</v>
+        <v>15.64756113114178</v>
       </c>
       <c r="E4" t="n">
-        <v>18.39796016486666</v>
+        <v>18.11246928918461</v>
       </c>
       <c r="F4" t="n">
-        <v>20.86286832290949</v>
+        <v>20.57737744722744</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.45805051087783</v>
+        <v>11.12973600384348</v>
       </c>
       <c r="C5" t="n">
-        <v>13.92295866892066</v>
+        <v>13.59464416188631</v>
       </c>
       <c r="D5" t="n">
-        <v>16.38786682696349</v>
+        <v>16.05955231992914</v>
       </c>
       <c r="E5" t="n">
-        <v>18.85277498500632</v>
+        <v>18.52446047797197</v>
       </c>
       <c r="F5" t="n">
-        <v>21.31768314304916</v>
+        <v>20.98936863601481</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.91286533101749</v>
+        <v>11.54172719263084</v>
       </c>
       <c r="C6" t="n">
-        <v>14.37777348906033</v>
+        <v>14.00663535067367</v>
       </c>
       <c r="D6" t="n">
-        <v>16.84268164710316</v>
+        <v>16.4715435087165</v>
       </c>
       <c r="E6" t="n">
-        <v>19.30758980514599</v>
+        <v>18.93645166675934</v>
       </c>
       <c r="F6" t="n">
-        <v>21.77249796318883</v>
+        <v>21.40135982480217</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>16.04</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>16.05</v>
+        <v>15.76</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1304,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $488,900/day is 12.2x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.29</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61361.17710389959</v>
+        <v>69689.8143823438</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.233902648773563</v>
+        <v>1.401381958714855</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69689.8143823438</v>
+        <v>69689.81438234381</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69689.81438234381</v>
+        <v>69689.8143823438</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.75</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>69689.8143823438</v>
+        <v>78561.62365720826</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.401381958714855</v>
+        <v>1.579783832347971</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.24</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78561.62365720826</v>
+        <v>95399.95554623679</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.579783832347971</v>
+        <v>1.918383306794497</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.17</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95399.95554623679</v>
+        <v>98658.98752475838</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.918383306794497</v>
+        <v>1.983918688945437</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>98658.98752475838</v>
+        <v>98658.9875247584</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.64756113114178</v>
+        <v>15.83371262147811</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.45740731010542</v>
+        <v>16.50498195047288</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.75792004689328</v>
+        <v>14.26741752049031</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31550</v>
+        <v>35425</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33287.5</v>
+        <v>36447</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.591674517581763</v>
+        <v>1.70392176668539</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>98658.9875247584</v>
+        <v>96705.01539499915</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.983918688945437</v>
+        <v>1.871067146909366</v>
       </c>
     </row>
   </sheetData>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1034.436005486279</v>
+        <v>1048.240727891962</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +743,7 @@
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>4775.442077512202</v>
+        <v>4789.246799917885</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.45740731010542</v>
+        <v>16.50498195047288</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.45740731010542</v>
+        <v>16.50498195047288</v>
       </c>
     </row>
     <row r="17">
@@ -803,7 +803,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38800</v>
+        <v>41313</v>
       </c>
       <c r="C2" t="n">
-        <v>38800</v>
+        <v>41313</v>
       </c>
       <c r="D2" t="n">
-        <v>1.344894531380352</v>
+        <v>1.402388192349907</v>
       </c>
       <c r="E2" t="n">
-        <v>0.672447265690176</v>
+        <v>0.7011940961749533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6551300000099703</v>
+        <v>0.6831365248583529</v>
       </c>
     </row>
     <row r="3">
@@ -869,19 +869,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37250</v>
+        <v>42125</v>
       </c>
       <c r="C3" t="n">
-        <v>37250</v>
+        <v>42125</v>
       </c>
       <c r="D3" t="n">
-        <v>1.306085215410569</v>
+        <v>1.429793307767013</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6530426077052844</v>
+        <v>0.7148966538835063</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6198406126705333</v>
+        <v>0.6785498751702369</v>
       </c>
     </row>
     <row r="4">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25875</v>
+        <v>28725</v>
       </c>
       <c r="C4" t="n">
-        <v>25875</v>
+        <v>28725</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6260085814194517</v>
+        <v>0.7007580421394621</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3130042907097259</v>
+        <v>0.3503790210697311</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2894396716721306</v>
+        <v>0.3240006345896213</v>
       </c>
     </row>
     <row r="5">
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31225</v>
+        <v>33625</v>
       </c>
       <c r="C5" t="n">
-        <v>31225</v>
+        <v>33625</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7536867006896918</v>
+        <v>0.8153799222706071</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3768433503448459</v>
+        <v>0.4076899611353035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3394985138241854</v>
+        <v>0.3672882532750482</v>
       </c>
     </row>
     <row r="6">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="C6" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5334023050829944</v>
+        <v>0.5942936688125495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2667011525414972</v>
+        <v>0.2971468344062748</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2340836976135177</v>
+        <v>0.26080588354844</v>
       </c>
     </row>
     <row r="7">
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="C7" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5312881789212163</v>
+        <v>0.5921795426507714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2656440894606081</v>
+        <v>0.2960897713253857</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2271515419242597</v>
+        <v>0.2531855620847016</v>
       </c>
     </row>
     <row r="8">
@@ -979,19 +979,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30750</v>
+        <v>33125</v>
       </c>
       <c r="C8" t="n">
-        <v>30750</v>
+        <v>33125</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5142241606154362</v>
+        <v>0.5751155243449912</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2571120803077181</v>
+        <v>0.2875577621724956</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2141939843080028</v>
+        <v>0.2395575607521192</v>
       </c>
     </row>
     <row r="9">
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30250</v>
+        <v>32625</v>
       </c>
       <c r="C9" t="n">
-        <v>30250</v>
+        <v>32625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4980661963789895</v>
+        <v>0.5589575601085446</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2490330981894947</v>
+        <v>0.2794787800542723</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2021208491108633</v>
+        <v>0.2268312475077285</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.781458871133463</v>
+        <v>3.033355541786249</v>
       </c>
     </row>
     <row r="11">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.88158471792154</v>
+        <v>14.20736433962441</v>
       </c>
       <c r="F11" t="n">
-        <v>10.97646117575982</v>
+        <v>11.23406197870406</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.75792004689328</v>
+        <v>14.26741752049031</v>
       </c>
     </row>
     <row r="13">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33287.5</v>
+        <v>36447</v>
       </c>
     </row>
   </sheetData>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.893762437481392</v>
+        <v>10.02847032256331</v>
       </c>
       <c r="C2" t="n">
-        <v>12.35867059552423</v>
+        <v>12.49778032245263</v>
       </c>
       <c r="D2" t="n">
-        <v>14.82357875356705</v>
+        <v>14.96709032234195</v>
       </c>
       <c r="E2" t="n">
-        <v>17.28848691160989</v>
+        <v>17.43640032223128</v>
       </c>
       <c r="F2" t="n">
-        <v>19.75339506965272</v>
+        <v>19.9057103221206</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.30575362626875</v>
+        <v>10.46178147213138</v>
       </c>
       <c r="C3" t="n">
-        <v>12.77066178431159</v>
+        <v>12.93109147202071</v>
       </c>
       <c r="D3" t="n">
-        <v>15.23556994235441</v>
+        <v>15.40040147191003</v>
       </c>
       <c r="E3" t="n">
-        <v>17.70047810039725</v>
+        <v>17.86971147179935</v>
       </c>
       <c r="F3" t="n">
-        <v>20.16538625844008</v>
+        <v>20.33902147168868</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.71774481505611</v>
+        <v>10.89509262169946</v>
       </c>
       <c r="C4" t="n">
-        <v>13.18265297309895</v>
+        <v>13.36440262158879</v>
       </c>
       <c r="D4" t="n">
-        <v>15.64756113114178</v>
+        <v>15.83371262147811</v>
       </c>
       <c r="E4" t="n">
-        <v>18.11246928918461</v>
+        <v>18.30302262136743</v>
       </c>
       <c r="F4" t="n">
-        <v>20.57737744722744</v>
+        <v>20.77233262125676</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.12973600384348</v>
+        <v>11.32840377126754</v>
       </c>
       <c r="C5" t="n">
-        <v>13.59464416188631</v>
+        <v>13.79771377115687</v>
       </c>
       <c r="D5" t="n">
-        <v>16.05955231992914</v>
+        <v>16.26702377104618</v>
       </c>
       <c r="E5" t="n">
-        <v>18.52446047797197</v>
+        <v>18.73633377093551</v>
       </c>
       <c r="F5" t="n">
-        <v>20.98936863601481</v>
+        <v>21.20564377082484</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.54172719263084</v>
+        <v>11.76171492083562</v>
       </c>
       <c r="C6" t="n">
-        <v>14.00663535067367</v>
+        <v>14.23102492072495</v>
       </c>
       <c r="D6" t="n">
-        <v>16.4715435087165</v>
+        <v>16.70033492061426</v>
       </c>
       <c r="E6" t="n">
-        <v>18.93645166675934</v>
+        <v>19.16964492050359</v>
       </c>
       <c r="F6" t="n">
-        <v>21.40135982480217</v>
+        <v>21.63895492039292</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.71</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.75</v>
+        <v>15.94</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.76</v>
+        <v>15.95</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96705.01539499915</v>
+        <v>96705.01539499914</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96705.01539499914</v>
+        <v>96705.01539499915</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/cmbt_fv_report.xlsx
+++ b/outputs/cmbt_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.83371262147811</v>
+        <v>15.94200751644991</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16.50498195047288</v>
+        <v>16.53942847316453</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.26741752049031</v>
+        <v>14.54802528411577</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35425</v>
+        <v>37300</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36447</v>
+        <v>38552.25</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.70392176668539</v>
+        <v>1.762020112070615</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96705.01539499915</v>
+        <v>96085.25800111341</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.871067146909366</v>
+        <v>1.81229437011037</v>
       </c>
     </row>
   </sheetData>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1048.240727891962</v>
+        <v>1058.236067424253</v>
       </c>
     </row>
     <row r="6">
@@ -743,7 +743,7 @@
         <v/>
       </c>
       <c r="B13" t="n">
-        <v>4789.246799917885</v>
+        <v>4799.242139450175</v>
       </c>
     </row>
     <row r="14">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16.50498195047288</v>
+        <v>16.53942847316453</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16.50498195047288</v>
+        <v>16.53942847316453</v>
       </c>
     </row>
     <row r="17">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41313</v>
+        <v>45250</v>
       </c>
       <c r="C2" t="n">
-        <v>41313</v>
+        <v>45250</v>
       </c>
       <c r="D2" t="n">
-        <v>1.402388192349907</v>
+        <v>1.503680507031041</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7011940961749533</v>
+        <v>0.7518402535155204</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6831365248583529</v>
+        <v>0.7324784119503854</v>
       </c>
     </row>
     <row r="3">
@@ -869,19 +869,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42125</v>
+        <v>44475</v>
       </c>
       <c r="C3" t="n">
-        <v>42125</v>
+        <v>44475</v>
       </c>
       <c r="D3" t="n">
-        <v>1.429793307767013</v>
+        <v>1.493072123969262</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7148966538835063</v>
+        <v>0.7465360619846308</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6785498751702369</v>
+        <v>0.7085806723502956</v>
       </c>
     </row>
     <row r="4">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28725</v>
+        <v>30125</v>
       </c>
       <c r="C4" t="n">
-        <v>28725</v>
+        <v>30125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7007580421394621</v>
+        <v>0.7399448806381344</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3503790210697311</v>
+        <v>0.3699724403190672</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3240006345896213</v>
+        <v>0.3421189575736392</v>
       </c>
     </row>
     <row r="5">
@@ -913,19 +913,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33625</v>
+        <v>34359</v>
       </c>
       <c r="C5" t="n">
-        <v>33625</v>
+        <v>34359</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8153799222706071</v>
+        <v>0.833437579872423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4076899611353035</v>
+        <v>0.4167187899362115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3672882532750482</v>
+        <v>0.3754223332758662</v>
       </c>
     </row>
     <row r="6">
@@ -935,19 +935,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="C6" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5942936688125495</v>
+        <v>0.6123377356033254</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2971468344062748</v>
+        <v>0.3061688678016627</v>
       </c>
       <c r="F6" t="n">
-        <v>0.26080588354844</v>
+        <v>0.268724525508026</v>
       </c>
     </row>
     <row r="7">
@@ -957,19 +957,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="C7" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5921795426507714</v>
+        <v>0.6102145489008539</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2960897713253857</v>
+        <v>0.305107274450427</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2531855620847016</v>
+        <v>0.2608964046007882</v>
       </c>
     </row>
     <row r="8">
@@ -979,19 +979,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33125</v>
+        <v>33858</v>
       </c>
       <c r="C8" t="n">
-        <v>33125</v>
+        <v>33858</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5751155243449912</v>
+        <v>0.5931505305950738</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2875577621724956</v>
+        <v>0.2965752652975369</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2395575607521192</v>
+        <v>0.2470698290226369</v>
       </c>
     </row>
     <row r="9">
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32625</v>
+        <v>33358</v>
       </c>
       <c r="C9" t="n">
-        <v>32625</v>
+        <v>33358</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5589575601085446</v>
+        <v>0.5769925663586271</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2794787800542723</v>
+        <v>0.2884962831793135</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2268312475077285</v>
+        <v>0.2341500553358603</v>
       </c>
     </row>
     <row r="10">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.033355541786249</v>
+        <v>3.169441189617498</v>
       </c>
     </row>
     <row r="11">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14.20736433962441</v>
+        <v>14.39013690738432</v>
       </c>
       <c r="F11" t="n">
-        <v>11.23406197870406</v>
+        <v>11.37858409449828</v>
       </c>
     </row>
     <row r="12">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.26741752049031</v>
+        <v>14.54802528411577</v>
       </c>
     </row>
     <row r="13">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36447</v>
+        <v>38552.25</v>
       </c>
     </row>
   </sheetData>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.02847032256331</v>
+        <v>10.10753700783517</v>
       </c>
       <c r="C2" t="n">
-        <v>12.49778032245263</v>
+        <v>12.58010726651609</v>
       </c>
       <c r="D2" t="n">
-        <v>14.96709032234195</v>
+        <v>15.05267752519701</v>
       </c>
       <c r="E2" t="n">
-        <v>17.43640032223128</v>
+        <v>17.52524778387794</v>
       </c>
       <c r="F2" t="n">
-        <v>19.9057103221206</v>
+        <v>19.99781804255887</v>
       </c>
     </row>
     <row r="3">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.46178147213138</v>
+        <v>10.55220200346161</v>
       </c>
       <c r="C3" t="n">
-        <v>12.93109147202071</v>
+        <v>13.02477226214254</v>
       </c>
       <c r="D3" t="n">
-        <v>15.40040147191003</v>
+        <v>15.49734252082346</v>
       </c>
       <c r="E3" t="n">
-        <v>17.86971147179935</v>
+        <v>17.96991277950438</v>
       </c>
       <c r="F3" t="n">
-        <v>20.33902147168868</v>
+        <v>20.44248303818531</v>
       </c>
     </row>
     <row r="4">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.89509262169946</v>
+        <v>10.99686699908806</v>
       </c>
       <c r="C4" t="n">
-        <v>13.36440262158879</v>
+        <v>13.46943725776898</v>
       </c>
       <c r="D4" t="n">
-        <v>15.83371262147811</v>
+        <v>15.94200751644991</v>
       </c>
       <c r="E4" t="n">
-        <v>18.30302262136743</v>
+        <v>18.41457777513083</v>
       </c>
       <c r="F4" t="n">
-        <v>20.77233262125676</v>
+        <v>20.88714803381176</v>
       </c>
     </row>
     <row r="5">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.32840377126754</v>
+        <v>11.4415319947145</v>
       </c>
       <c r="C5" t="n">
-        <v>13.79771377115687</v>
+        <v>13.91410225339543</v>
       </c>
       <c r="D5" t="n">
-        <v>16.26702377104618</v>
+        <v>16.38667251207635</v>
       </c>
       <c r="E5" t="n">
-        <v>18.73633377093551</v>
+        <v>18.85924277075728</v>
       </c>
       <c r="F5" t="n">
-        <v>21.20564377082484</v>
+        <v>21.3318130294382</v>
       </c>
     </row>
     <row r="6">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.76171492083562</v>
+        <v>11.88619699034095</v>
       </c>
       <c r="C6" t="n">
-        <v>14.23102492072495</v>
+        <v>14.35876724902187</v>
       </c>
       <c r="D6" t="n">
-        <v>16.70033492061426</v>
+        <v>16.8313375077028</v>
       </c>
       <c r="E6" t="n">
-        <v>19.16964492050359</v>
+        <v>19.30390776638372</v>
       </c>
       <c r="F6" t="n">
-        <v>21.63895492039292</v>
+        <v>21.77647802506465</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1258,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.91</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="3">
@@ -1266,7 +1266,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.94</v>
+        <v>16.05</v>
       </c>
     </row>
     <row r="4">
@@ -1274,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.95</v>
+        <v>16.07</v>
       </c>
     </row>
   </sheetData>
